--- a/docs/demo/facturas-ejemplo.xlsx
+++ b/docs/demo/facturas-ejemplo.xlsx
@@ -56,7 +56,7 @@
     <x:t>Total</x:t>
   </x:si>
   <x:si>
-    <x:t>01a163c1-f362-762f-973b-a2ae6ea5958a</x:t>
+    <x:t>01a163cf-f6c6-73b3-a4fb-6c4b44aee663</x:t>
   </x:si>
   <x:si>
     <x:t>sample-09.pdf</x:t>
@@ -83,7 +83,7 @@
     <x:t>USD</x:t>
   </x:si>
   <x:si>
-    <x:t>01a163c1-f36a-7c24-a7a8-6663d2a7b6d2</x:t>
+    <x:t>01a163cf-f6c9-7edf-8d6c-420eecec9bd7</x:t>
   </x:si>
   <x:si>
     <x:t>sample-10.png</x:t>
@@ -101,7 +101,7 @@
     <x:t>INV-001270</x:t>
   </x:si>
   <x:si>
-    <x:t>01a163c1-f36b-7f81-a779-f53affad2516</x:t>
+    <x:t>01a163cf-f6cb-7d7c-9d11-35f5d6fc6af2</x:t>
   </x:si>
   <x:si>
     <x:t>sample-11.jpg</x:t>

--- a/docs/demo/facturas-ejemplo.xlsx
+++ b/docs/demo/facturas-ejemplo.xlsx
@@ -56,7 +56,7 @@
     <x:t>Total</x:t>
   </x:si>
   <x:si>
-    <x:t>01a163cf-f6c6-73b3-a4fb-6c4b44aee663</x:t>
+    <x:t>01a16458-2238-71a7-b384-681fb17fc030</x:t>
   </x:si>
   <x:si>
     <x:t>sample-09.pdf</x:t>
@@ -83,7 +83,7 @@
     <x:t>USD</x:t>
   </x:si>
   <x:si>
-    <x:t>01a163cf-f6c9-7edf-8d6c-420eecec9bd7</x:t>
+    <x:t>01a16458-223e-7fcc-ae14-795888396781</x:t>
   </x:si>
   <x:si>
     <x:t>sample-10.png</x:t>
@@ -101,7 +101,7 @@
     <x:t>INV-001270</x:t>
   </x:si>
   <x:si>
-    <x:t>01a163cf-f6cb-7d7c-9d11-35f5d6fc6af2</x:t>
+    <x:t>01a16458-2240-7d74-b4cb-36170ec1aa4b</x:t>
   </x:si>
   <x:si>
     <x:t>sample-11.jpg</x:t>
